--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/CoreOrganizacionCl</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -684,10 +684,10 @@
 </t>
   </si>
   <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
+    <t>Estado de si es una Organización Validada o no (true|false)</t>
+  </si>
+  <si>
+    <t>Indicador si una organización sigue vigente en su rol dentro del sistema de salud</t>
   </si>
   <si>
     <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
@@ -750,10 +750,10 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
-  </si>
-  <si>
-    <t>A name associated with the organization.</t>
+    <t>Nombre Legal de la Organizacion</t>
+  </si>
+  <si>
+    <t>Nombre Legal de la Organización</t>
   </si>
   <si>
     <t>If the name of an organization changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
@@ -774,10 +774,10 @@
     <t>Organization.alias</t>
   </si>
   <si>
-    <t>A list of alternate names that the organization is known as, or was known as in the past</t>
-  </si>
-  <si>
-    <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
+    <t>Nombre de Fantasía</t>
+  </si>
+  <si>
+    <t>Nombre por lo que  popularmente es conocida la Organización y que no corresponde al nombre legal</t>
   </si>
   <si>
     <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the organization.</t>
@@ -794,10 +794,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
-  </si>
-  <si>
-    <t>A contact detail for the organization.</t>
+    <t>Contactos de la organización</t>
   </si>
   <si>
     <t>The use code 'home' is not to be used. Note that these contacts are not the contact details of people who are employed by or represent the organization, but official contacts for the organization itself.</t>
@@ -823,6 +820,131 @@
     <t>./ContactPoints</t>
   </si>
   <si>
+    <t>Organization.telecom.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.system</t>
+  </si>
+  <si>
+    <t>phone | fax | email | pager | url | sms | other</t>
+  </si>
+  <si>
+    <t>Forma de telecomunicación para el punto de contacto: qué sistema de comunicación se requiere para hacer uso del contacto.</t>
+  </si>
+  <si>
+    <t>VS HL7 FHIR tipos diferentes de medios de contacto</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system</t>
+  </si>
+  <si>
+    <t>ContactPoint.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpt-2
+</t>
+  </si>
+  <si>
+    <t>XTN.3</t>
+  </si>
+  <si>
+    <t>./scheme</t>
+  </si>
+  <si>
+    <t>./ContactPointType</t>
+  </si>
+  <si>
+    <t>Organization.telecom.value</t>
+  </si>
+  <si>
+    <t>Dato del contato de la ubicación descrita</t>
+  </si>
+  <si>
+    <t>Valor del contacto como por ejemplo el numero de telefono fijo o de móvil o el email de Organiación</t>
+  </si>
+  <si>
+    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
+  </si>
+  <si>
+    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+  </si>
+  <si>
+    <t>ContactPoint.value</t>
+  </si>
+  <si>
+    <t>XTN.1 (or XTN.12)</t>
+  </si>
+  <si>
+    <t>./url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | mobile - purpose of this contact point</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for the contact point.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use</t>
+  </si>
+  <si>
+    <t>ContactPoint.use</t>
+  </si>
+  <si>
+    <t>XTN.2 - but often indicated by field</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./ContactPointPurpose</t>
+  </si>
+  <si>
+    <t>Organization.telecom.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+  </si>
+  <si>
+    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
+  </si>
+  <si>
+    <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>Organization.telecom.period</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use.</t>
+  </si>
+  <si>
+    <t>ContactPoint.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
     <t>Organization.address</t>
   </si>
   <si>
@@ -830,10 +952,10 @@
 </t>
   </si>
   <si>
-    <t>An address for the organization</t>
-  </si>
-  <si>
-    <t>An address for the organization.</t>
+    <t>Dirección de la Localiación</t>
+  </si>
+  <si>
+    <t>Se definirá la dirección en una línea y se podría codificar en city la comuna, en district la provincia y en state la región</t>
   </si>
   <si>
     <t>Organization may have multiple addresses with different uses or applicable periods. The use code 'home' is not to be used.</t>
@@ -859,6 +981,298 @@
     <t>./PrimaryAddress and ./OtherAddresses</t>
   </si>
   <si>
+    <t>Organization.address.id</t>
+  </si>
+  <si>
+    <t>Organization.address.extension</t>
+  </si>
+  <si>
+    <t>Organization.address.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | billing - purpose of this address</t>
+  </si>
+  <si>
+    <t>The purpose of this address.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows an appropriate address to be chosen from a list of many.</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>The use of an address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.use</t>
+  </si>
+  <si>
+    <t>XAD.7</t>
+  </si>
+  <si>
+    <t>./AddressPurpose</t>
+  </si>
+  <si>
+    <t>Organization.address.type</t>
+  </si>
+  <si>
+    <t>postal | physical | both</t>
+  </si>
+  <si>
+    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
+  </si>
+  <si>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>The type of an address (physical / postal).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.type</t>
+  </si>
+  <si>
+    <t>XAD.18</t>
+  </si>
+  <si>
+    <t>Organization.address.text</t>
+  </si>
+  <si>
+    <t>Text representation of the address</t>
+  </si>
+  <si>
+    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street, Erewhon 9132</t>
+  </si>
+  <si>
+    <t>Address.text</t>
+  </si>
+  <si>
+    <t>XAD.1 + XAD.2 + XAD.3 + XAD.4 + XAD.5 + XAD.6</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Organization.address.line</t>
+  </si>
+  <si>
+    <t>Calle o avenida, numero y casa o depto</t>
+  </si>
+  <si>
+    <t>Aquí se escribe toda la dirección completa</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street</t>
+  </si>
+  <si>
+    <t>Address.line</t>
+  </si>
+  <si>
+    <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = AL]</t>
+  </si>
+  <si>
+    <t>./StreetAddress (newline delimitted)</t>
+  </si>
+  <si>
+    <t>Organization.address.city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municpality
+</t>
+  </si>
+  <si>
+    <t>Campo para Comuna de residencia</t>
+  </si>
+  <si>
+    <t>Campo para Comuna de residencia. Se usa el valueSet de códigos de comunas definidos a nivel naciona.</t>
+  </si>
+  <si>
+    <t>Erewhon</t>
+  </si>
+  <si>
+    <t>Códigos Comuna, Ministerio del Interior, 2018</t>
+  </si>
+  <si>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosComunaCL</t>
+  </si>
+  <si>
+    <t>Address.city</t>
+  </si>
+  <si>
+    <t>XAD.3</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CTY]</t>
+  </si>
+  <si>
+    <t>./Jurisdiction</t>
+  </si>
+  <si>
+    <t>Organization.address.district</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County
+</t>
+  </si>
+  <si>
+    <t>Campo para Provincia de Residencia</t>
+  </si>
+  <si>
+    <t>Campo para Provincia de Residencia. Se usa el valueSet de códigos de provicias definidos a nivel naciona.</t>
+  </si>
+  <si>
+    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Códigos Provincia, Ministerio del Interior, 2018</t>
+  </si>
+  <si>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosProvinciasCL</t>
+  </si>
+  <si>
+    <t>Address.district</t>
+  </si>
+  <si>
+    <t>XAD.9</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT | CPA]</t>
+  </si>
+  <si>
+    <t>Organization.address.state</t>
+  </si>
+  <si>
+    <t>Province
+Territory</t>
+  </si>
+  <si>
+    <t>Campo para la Región</t>
+  </si>
+  <si>
+    <t>Campo Región. Se usa el valueSet de códigos de regiones definidos a nivel naciona.</t>
+  </si>
+  <si>
+    <t>Códigos Regiones, Ministerio del Interior, 2018</t>
+  </si>
+  <si>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosRegionesCL</t>
+  </si>
+  <si>
+    <t>Address.state</t>
+  </si>
+  <si>
+    <t>XAD.4</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = STA]</t>
+  </si>
+  <si>
+    <t>./Region</t>
+  </si>
+  <si>
+    <t>Organization.address.postalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip
+</t>
+  </si>
+  <si>
+    <t>Postal code for area</t>
+  </si>
+  <si>
+    <t>A postal code designating a region defined by the postal service.</t>
+  </si>
+  <si>
+    <t>9132</t>
+  </si>
+  <si>
+    <t>Address.postalCode</t>
+  </si>
+  <si>
+    <t>XAD.5</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = ZIP]</t>
+  </si>
+  <si>
+    <t>./PostalIdentificationCode</t>
+  </si>
+  <si>
+    <t>Organization.address.country</t>
+  </si>
+  <si>
+    <t>Campo para País de Residencia</t>
+  </si>
+  <si>
+    <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
+  </si>
+  <si>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/CodPais</t>
+  </si>
+  <si>
+    <t>Address.country</t>
+  </si>
+  <si>
+    <t>XAD.6</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT]</t>
+  </si>
+  <si>
+    <t>./Country</t>
+  </si>
+  <si>
+    <t>Organization.address.period</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use.</t>
+  </si>
+  <si>
+    <t>Allows addresses to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
+  &lt;start value="2010-03-23"/&gt;
+  &lt;end value="2010-07-01"/&gt;
+&lt;/valuePeriod&gt;</t>
+  </si>
+  <si>
+    <t>Address.period</t>
+  </si>
+  <si>
+    <t>XAD.12 / XAD.13 + XAD.14</t>
+  </si>
+  <si>
     <t>Organization.partOf</t>
   </si>
   <si>
@@ -881,10 +1295,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
-  </si>
-  <si>
-    <t>Contact for the organization for a certain purpose.</t>
+    <t>Contacto de la Organización para ciertos propósitos</t>
   </si>
   <si>
     <t>Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
@@ -922,16 +1333,16 @@
     <t>Organization.contact.purpose</t>
   </si>
   <si>
-    <t>The type of contact</t>
-  </si>
-  <si>
-    <t>Indicates a purpose for which the contact can be reached.</t>
+    <t>El tipo de contacto</t>
+  </si>
+  <si>
+    <t>El propósito mediante el cual el contacto puede ser alcanzado</t>
   </si>
   <si>
     <t>Need to distinguish between multiple contact persons.</t>
   </si>
   <si>
-    <t>The purpose for which you would contact a contact party.</t>
+    <t>Códigos del propósito del contacto, HL7 FHIR</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
@@ -947,10 +1358,7 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the contact</t>
-  </si>
-  <si>
-    <t>A name associated with the contact.</t>
+    <t>Nombre asociado al contacto</t>
   </si>
   <si>
     <t>Need to be able to track the person by name.</t>
@@ -965,10 +1373,10 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>Contact details (telephone, email, etc.)  for a contact</t>
-  </si>
-  <si>
-    <t>A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
+    <t>Detalles de contacto de la Organización</t>
+  </si>
+  <si>
+    <t>Detalles del contacto de la Organización comunmente el o los mas usados (Ej: Teléfono fijo, móvil, email, etc.)</t>
   </si>
   <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
@@ -978,6 +1386,39 @@
   </si>
   <si>
     <t>./telecom</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.system</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.value</t>
+  </si>
+  <si>
+    <t>Dato del contato del paciente descrito</t>
+  </si>
+  <si>
+    <t>Valor del contacto como por ejemplo el numero de telefono fijo o de móvil o el email del Paciente</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | mobile</t>
+  </si>
+  <si>
+    <t>Propósito para el contacto que se ha definido</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.rank</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.period</t>
   </si>
   <si>
     <t>Organization.contact.address</t>
@@ -1320,10 +1761,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM35"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.77734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1333,7 +1774,7 @@
     <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1347,7 +1788,7 @@
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.6484375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="60.84375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1358,7 +1799,7 @@
     <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="36" max="36" width="31.1328125" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="218.1953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -3037,7 +3478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -3053,7 +3494,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -3709,7 +4150,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>235</v>
       </c>
@@ -3725,7 +4166,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3822,7 +4263,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>243</v>
       </c>
@@ -3838,7 +4279,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3935,7 +4376,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>248</v>
       </c>
@@ -3951,7 +4392,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3966,13 +4407,13 @@
         <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>73</v>
@@ -4030,19 +4471,19 @@
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AI24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AI24" t="s" s="2">
+      <c r="AJ24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>73</v>
@@ -4050,7 +4491,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4061,7 +4502,7 @@
         <v>74</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>73</v>
@@ -4073,20 +4514,16 @@
         <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>260</v>
+        <v>148</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>149</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>73</v>
       </c>
@@ -4134,28 +4571,28 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>73</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>73</v>
@@ -4163,18 +4600,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>73</v>
@@ -4183,21 +4620,21 @@
         <v>73</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>205</v>
+        <v>127</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>128</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M26" s="2"/>
-      <c r="N26" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>73</v>
       </c>
@@ -4233,40 +4670,40 @@
         <v>73</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="AC26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>274</v>
+        <v>152</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>73</v>
@@ -4274,7 +4711,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4285,7 +4722,7 @@
         <v>74</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>73</v>
@@ -4294,23 +4731,19 @@
         <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>73</v>
       </c>
@@ -4334,13 +4767,13 @@
         <v>73</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4358,28 +4791,28 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>269</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>73</v>
@@ -4387,7 +4820,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4407,19 +4840,23 @@
         <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>148</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O28" t="s" s="2">
         <v>73</v>
       </c>
@@ -4467,7 +4904,7 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
@@ -4479,16 +4916,16 @@
         <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>276</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>152</v>
+        <v>277</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>73</v>
@@ -4496,41 +4933,43 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>128</v>
+        <v>279</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>280</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O29" t="s" s="2">
         <v>73</v>
       </c>
@@ -4554,13 +4993,11 @@
         <v>73</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="X29" s="2"/>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>283</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -4578,28 +5015,28 @@
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>158</v>
+        <v>284</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>73</v>
@@ -4607,43 +5044,41 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>127</v>
+        <v>289</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>73</v>
       </c>
@@ -4691,25 +5126,25 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4720,7 +5155,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4740,21 +5175,19 @@
         <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M31" s="2"/>
-      <c r="N31" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>73</v>
       </c>
@@ -4778,13 +5211,13 @@
         <v>73</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>293</v>
+        <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4802,7 +5235,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -4817,21 +5250,21 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4842,10 +5275,10 @@
         <v>74</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4854,17 +5287,19 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M32" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>73</v>
@@ -4913,28 +5348,28 @@
         <v>73</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>73</v>
+        <v>305</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>93</v>
+        <v>306</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>73</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>73</v>
@@ -4942,7 +5377,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -4953,7 +5388,7 @@
         <v>74</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>73</v>
@@ -4965,18 +5400,16 @@
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>249</v>
+        <v>148</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>150</v>
       </c>
       <c r="M33" s="2"/>
-      <c r="N33" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>73</v>
       </c>
@@ -5024,25 +5457,25 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>303</v>
+        <v>151</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>152</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5053,18 +5486,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>73</v>
@@ -5076,18 +5509,18 @@
         <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>310</v>
+        <v>128</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M34" s="2"/>
-      <c r="N34" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5123,37 +5556,37 @@
         <v>73</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>309</v>
+        <v>158</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>313</v>
+        <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>314</v>
+        <v>152</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5162,9 +5595,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5175,29 +5608,31 @@
         <v>74</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M35" s="2"/>
-      <c r="N35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>73</v>
@@ -5210,7 +5645,7 @@
         <v>73</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>73</v>
+        <v>317</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>73</v>
@@ -5222,13 +5657,13 @@
         <v>73</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>318</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5246,13 +5681,13 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>73</v>
@@ -5261,20 +5696,2894 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>73</v>
+        <v>321</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P36" s="2"/>
+      <c r="Q36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P37" s="2"/>
+      <c r="Q37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P41" s="2"/>
+      <c r="Q41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P42" s="2"/>
+      <c r="Q42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X43" s="2"/>
+      <c r="Y43" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="N45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P45" s="2"/>
+      <c r="Q45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AM45" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P47" s="2"/>
+      <c r="Q47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X55" s="2"/>
+      <c r="Y55" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P56" s="2"/>
+      <c r="Q56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="X57" s="2"/>
+      <c r="Y57" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P60" s="2"/>
+      <c r="Q60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M61" s="2"/>
+      <c r="N61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM35">
+  <autoFilter ref="A1:AM61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5284,7 +8593,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-OrganizationLE.xlsx
+++ b/StructureDefinition-OrganizationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
